--- a/template.xlsx
+++ b/template.xlsx
@@ -326,8 +326,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yy"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="dd\-mmm"/>
+    <numFmt numFmtId="166" formatCode="dd\-mmm"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="19">
@@ -723,6 +723,15 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -832,15 +841,6 @@
       <bottom style="medium">
         <color rgb="FFCCCCCC"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -1246,63 +1246,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1318,7 +1322,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1326,11 +1330,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1338,18 +1342,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1358,51 +1358,51 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="41" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="41" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1414,7 +1414,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1426,11 +1426,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1446,11 +1446,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1755,7 +1755,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="11.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="11.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="11.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="51"/>
   </cols>
   <sheetData>
@@ -2002,956 +2002,956 @@
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="35" t="n">
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="36" t="n">
         <f aca="false">(I7-H7)/8.5*1.33</f>
         <v>0</v>
       </c>
-      <c r="K7" s="36"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="43"/>
-      <c r="W7" s="44" t="n">
+      <c r="K7" s="37"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="44"/>
+      <c r="W7" s="45" t="n">
         <f aca="false">SUM(N7:V7)</f>
         <v>0</v>
       </c>
-      <c r="X7" s="45"/>
-      <c r="Y7" s="46"/>
-      <c r="Z7" s="47" t="n">
+      <c r="X7" s="46"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="48" t="n">
         <f aca="false">W7+X7+Y7</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="48"/>
+      <c r="AA7" s="49"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="33"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="35" t="n">
+      <c r="B8" s="34"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="36" t="n">
         <f aca="false">(I8-H8/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K8" s="50"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="52"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="41"/>
-      <c r="S8" s="42"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="43"/>
-      <c r="W8" s="44" t="n">
+      <c r="K8" s="51"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="42"/>
+      <c r="U8" s="42"/>
+      <c r="V8" s="44"/>
+      <c r="W8" s="45" t="n">
         <f aca="false">SUM(N8:V8)</f>
         <v>0</v>
       </c>
-      <c r="X8" s="45"/>
-      <c r="Y8" s="46"/>
-      <c r="Z8" s="47" t="n">
+      <c r="X8" s="46"/>
+      <c r="Y8" s="47"/>
+      <c r="Z8" s="48" t="n">
         <f aca="false">W8+X8+Y8</f>
         <v>0</v>
       </c>
-      <c r="AA8" s="48"/>
+      <c r="AA8" s="49"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="35" t="n">
+      <c r="B9" s="34"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="36" t="n">
         <f aca="false">(I9-H9/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K9" s="50"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="42"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="44" t="n">
+      <c r="K9" s="51"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="42"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="45" t="n">
         <f aca="false">SUM(N9:V9)</f>
         <v>0</v>
       </c>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="46"/>
-      <c r="Z9" s="47" t="n">
+      <c r="X9" s="46"/>
+      <c r="Y9" s="47"/>
+      <c r="Z9" s="48" t="n">
         <f aca="false">W9+X9+Y9</f>
         <v>0</v>
       </c>
-      <c r="AA9" s="48"/>
+      <c r="AA9" s="49"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="33"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="35" t="n">
+      <c r="B10" s="34"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="36" t="n">
         <f aca="false">(I10-H10/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K10" s="50"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="44" t="n">
+      <c r="K10" s="51"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="42"/>
+      <c r="U10" s="42"/>
+      <c r="V10" s="44"/>
+      <c r="W10" s="45" t="n">
         <f aca="false">SUM(N10:V10)</f>
         <v>0</v>
       </c>
-      <c r="X10" s="45"/>
-      <c r="Y10" s="46"/>
-      <c r="Z10" s="47" t="n">
+      <c r="X10" s="46"/>
+      <c r="Y10" s="47"/>
+      <c r="Z10" s="48" t="n">
         <f aca="false">W10+X10+Y10</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="48"/>
+      <c r="AA10" s="49"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="35" t="n">
+      <c r="B11" s="34"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="36" t="n">
         <f aca="false">(I11-H11/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K11" s="50"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="41"/>
-      <c r="S11" s="42"/>
-      <c r="T11" s="41"/>
-      <c r="U11" s="41"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="44" t="n">
+      <c r="K11" s="51"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="41"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="42"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="45" t="n">
         <f aca="false">SUM(N11:V11)</f>
         <v>0</v>
       </c>
-      <c r="X11" s="45"/>
-      <c r="Y11" s="46"/>
-      <c r="Z11" s="47" t="n">
+      <c r="X11" s="46"/>
+      <c r="Y11" s="47"/>
+      <c r="Z11" s="48" t="n">
         <f aca="false">W11+X11+Y11</f>
         <v>0</v>
       </c>
-      <c r="AA11" s="48"/>
+      <c r="AA11" s="49"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="33"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="35" t="n">
+      <c r="B12" s="34"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="36" t="n">
         <f aca="false">(I12-H12/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K12" s="50"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="55"/>
-      <c r="R12" s="41"/>
-      <c r="S12" s="56"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="44" t="n">
+      <c r="K12" s="51"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="56"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="57"/>
+      <c r="T12" s="42"/>
+      <c r="U12" s="42"/>
+      <c r="V12" s="44"/>
+      <c r="W12" s="45" t="n">
         <f aca="false">SUM(N12:V12)</f>
         <v>0</v>
       </c>
-      <c r="X12" s="45"/>
-      <c r="Y12" s="46"/>
-      <c r="Z12" s="47" t="n">
+      <c r="X12" s="46"/>
+      <c r="Y12" s="47"/>
+      <c r="Z12" s="48" t="n">
         <f aca="false">W12+X12+Y12</f>
         <v>0</v>
       </c>
-      <c r="AA12" s="48"/>
+      <c r="AA12" s="49"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="35" t="n">
+      <c r="B13" s="34"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="36" t="n">
         <f aca="false">(I13-H13/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K13" s="50"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="41"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="41"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="44" t="n">
+      <c r="K13" s="51"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="42"/>
+      <c r="V13" s="44"/>
+      <c r="W13" s="45" t="n">
         <f aca="false">SUM(N13:V13)</f>
         <v>0</v>
       </c>
-      <c r="X13" s="45"/>
-      <c r="Y13" s="46"/>
-      <c r="Z13" s="47" t="n">
+      <c r="X13" s="46"/>
+      <c r="Y13" s="47"/>
+      <c r="Z13" s="48" t="n">
         <f aca="false">W13+X13+Y13</f>
         <v>0</v>
       </c>
-      <c r="AA13" s="48"/>
+      <c r="AA13" s="49"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="35" t="n">
+      <c r="B14" s="34"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="36" t="n">
         <f aca="false">(I14-H14/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K14" s="50"/>
-      <c r="L14" s="51"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="40"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="41"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="44" t="n">
+      <c r="K14" s="51"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="42"/>
+      <c r="U14" s="42"/>
+      <c r="V14" s="44"/>
+      <c r="W14" s="45" t="n">
         <f aca="false">SUM(N14:V14)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="45"/>
-      <c r="Y14" s="46"/>
-      <c r="Z14" s="47" t="n">
+      <c r="X14" s="46"/>
+      <c r="Y14" s="47"/>
+      <c r="Z14" s="48" t="n">
         <f aca="false">W14+X14+Y14</f>
         <v>0</v>
       </c>
-      <c r="AA14" s="48"/>
+      <c r="AA14" s="49"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="35" t="n">
+      <c r="B15" s="34"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="36" t="n">
         <f aca="false">(I15-H15/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K15" s="50"/>
-      <c r="L15" s="51"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="41"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="44" t="n">
+      <c r="K15" s="51"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="42"/>
+      <c r="U15" s="42"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="45" t="n">
         <f aca="false">SUM(N15:V15)</f>
         <v>0</v>
       </c>
-      <c r="X15" s="45"/>
-      <c r="Y15" s="46"/>
-      <c r="Z15" s="47" t="n">
+      <c r="X15" s="46"/>
+      <c r="Y15" s="47"/>
+      <c r="Z15" s="48" t="n">
         <f aca="false">W15+X15+Y15</f>
         <v>0</v>
       </c>
-      <c r="AA15" s="48"/>
+      <c r="AA15" s="49"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="33"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="35" t="n">
+      <c r="B16" s="34"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="36" t="n">
         <f aca="false">(I16-H16/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K16" s="50"/>
-      <c r="L16" s="51"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="44" t="n">
+      <c r="K16" s="51"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="42"/>
+      <c r="U16" s="42"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="45" t="n">
         <f aca="false">SUM(N16:V16)</f>
         <v>0</v>
       </c>
-      <c r="X16" s="45"/>
-      <c r="Y16" s="46"/>
-      <c r="Z16" s="47" t="n">
+      <c r="X16" s="46"/>
+      <c r="Y16" s="47"/>
+      <c r="Z16" s="48" t="n">
         <f aca="false">W16+X16+Y16</f>
         <v>0</v>
       </c>
-      <c r="AA16" s="48"/>
+      <c r="AA16" s="49"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="33"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="35" t="n">
+      <c r="B17" s="34"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="36" t="n">
         <f aca="false">(I17-H17/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K17" s="50"/>
-      <c r="L17" s="51"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="41"/>
-      <c r="V17" s="43"/>
-      <c r="W17" s="44" t="n">
+      <c r="K17" s="51"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="42"/>
+      <c r="U17" s="42"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="45" t="n">
         <f aca="false">SUM(N17:V17)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="45"/>
-      <c r="Y17" s="46"/>
-      <c r="Z17" s="47" t="n">
+      <c r="X17" s="46"/>
+      <c r="Y17" s="47"/>
+      <c r="Z17" s="48" t="n">
         <f aca="false">W17+X17+Y17</f>
         <v>0</v>
       </c>
-      <c r="AA17" s="48"/>
+      <c r="AA17" s="49"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="35" t="n">
+      <c r="B18" s="34"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="36" t="n">
         <f aca="false">(I18-H18/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K18" s="50"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="40"/>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="41"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="41"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="44" t="n">
+      <c r="K18" s="51"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="41"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="42"/>
+      <c r="U18" s="42"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="45" t="n">
         <f aca="false">SUM(N18:V18)</f>
         <v>0</v>
       </c>
-      <c r="X18" s="45"/>
-      <c r="Y18" s="46"/>
-      <c r="Z18" s="47" t="n">
+      <c r="X18" s="46"/>
+      <c r="Y18" s="47"/>
+      <c r="Z18" s="48" t="n">
         <f aca="false">W18+X18+Y18</f>
         <v>0</v>
       </c>
-      <c r="AA18" s="48"/>
+      <c r="AA18" s="49"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="33"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="35" t="n">
+      <c r="B19" s="34"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="36" t="n">
         <f aca="false">(I19-H19/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K19" s="50"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="41"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="41"/>
-      <c r="V19" s="43"/>
-      <c r="W19" s="44" t="n">
+      <c r="K19" s="51"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="42"/>
+      <c r="U19" s="42"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="45" t="n">
         <f aca="false">SUM(N19:V19)</f>
         <v>0</v>
       </c>
-      <c r="X19" s="45"/>
-      <c r="Y19" s="46"/>
-      <c r="Z19" s="47" t="n">
+      <c r="X19" s="46"/>
+      <c r="Y19" s="47"/>
+      <c r="Z19" s="48" t="n">
         <f aca="false">W19+X19+Y19</f>
         <v>0</v>
       </c>
-      <c r="AA19" s="48"/>
+      <c r="AA19" s="49"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="33"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="35" t="n">
+      <c r="B20" s="34"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="36" t="n">
         <f aca="false">(I20-H20/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K20" s="50"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="40"/>
-      <c r="R20" s="41"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="41"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="44" t="n">
+      <c r="K20" s="51"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="42"/>
+      <c r="U20" s="42"/>
+      <c r="V20" s="44"/>
+      <c r="W20" s="45" t="n">
         <f aca="false">SUM(N20:V20)</f>
         <v>0</v>
       </c>
-      <c r="X20" s="45"/>
-      <c r="Y20" s="46"/>
-      <c r="Z20" s="47" t="n">
+      <c r="X20" s="46"/>
+      <c r="Y20" s="47"/>
+      <c r="Z20" s="48" t="n">
         <f aca="false">W20+X20+Y20</f>
         <v>0</v>
       </c>
-      <c r="AA20" s="48"/>
+      <c r="AA20" s="49"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="33"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="35" t="n">
+      <c r="B21" s="34"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="36" t="n">
         <f aca="false">(I21-H21/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K21" s="50"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="40"/>
-      <c r="Q21" s="40"/>
-      <c r="R21" s="41"/>
-      <c r="S21" s="42"/>
-      <c r="T21" s="41"/>
-      <c r="U21" s="41"/>
-      <c r="V21" s="43"/>
-      <c r="W21" s="44" t="n">
+      <c r="K21" s="51"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="41"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="42"/>
+      <c r="U21" s="42"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="45" t="n">
         <f aca="false">SUM(N21:V21)</f>
         <v>0</v>
       </c>
-      <c r="X21" s="45"/>
-      <c r="Y21" s="46"/>
-      <c r="Z21" s="47" t="n">
+      <c r="X21" s="46"/>
+      <c r="Y21" s="47"/>
+      <c r="Z21" s="48" t="n">
         <f aca="false">W21+X21+Y21</f>
         <v>0</v>
       </c>
-      <c r="AA21" s="48"/>
+      <c r="AA21" s="49"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="33"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="35" t="n">
+      <c r="B22" s="34"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="36" t="n">
         <f aca="false">(I22-H22/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K22" s="50"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="41"/>
-      <c r="S22" s="42"/>
-      <c r="T22" s="41"/>
-      <c r="U22" s="41"/>
-      <c r="V22" s="43"/>
-      <c r="W22" s="44" t="n">
+      <c r="K22" s="51"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="41"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="41"/>
+      <c r="R22" s="42"/>
+      <c r="S22" s="43"/>
+      <c r="T22" s="42"/>
+      <c r="U22" s="42"/>
+      <c r="V22" s="44"/>
+      <c r="W22" s="45" t="n">
         <f aca="false">SUM(N22:V22)</f>
         <v>0</v>
       </c>
-      <c r="X22" s="45"/>
-      <c r="Y22" s="46"/>
-      <c r="Z22" s="47" t="n">
+      <c r="X22" s="46"/>
+      <c r="Y22" s="47"/>
+      <c r="Z22" s="48" t="n">
         <f aca="false">W22+X22+Y22</f>
         <v>0</v>
       </c>
-      <c r="AA22" s="48"/>
+      <c r="AA22" s="49"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="35" t="n">
+      <c r="B23" s="34"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="36" t="n">
         <f aca="false">(I23-H23/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K23" s="50"/>
-      <c r="L23" s="51"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="41"/>
-      <c r="S23" s="42"/>
-      <c r="T23" s="41"/>
-      <c r="U23" s="41"/>
-      <c r="V23" s="43"/>
-      <c r="W23" s="44" t="n">
+      <c r="K23" s="51"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="41"/>
+      <c r="P23" s="41"/>
+      <c r="Q23" s="41"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="42"/>
+      <c r="U23" s="42"/>
+      <c r="V23" s="44"/>
+      <c r="W23" s="45" t="n">
         <f aca="false">SUM(N23:V23)</f>
         <v>0</v>
       </c>
-      <c r="X23" s="45"/>
-      <c r="Y23" s="46"/>
-      <c r="Z23" s="47" t="n">
+      <c r="X23" s="46"/>
+      <c r="Y23" s="47"/>
+      <c r="Z23" s="48" t="n">
         <f aca="false">W23+X23+Y23</f>
         <v>0</v>
       </c>
-      <c r="AA23" s="48"/>
+      <c r="AA23" s="49"/>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="33"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="35" t="n">
+      <c r="B24" s="34"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="36" t="n">
         <f aca="false">(I24-H24/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="40"/>
-      <c r="Q24" s="40"/>
-      <c r="R24" s="41"/>
-      <c r="S24" s="42"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="41"/>
-      <c r="V24" s="43"/>
-      <c r="W24" s="44" t="n">
+      <c r="K24" s="51"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="41"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="41"/>
+      <c r="R24" s="42"/>
+      <c r="S24" s="43"/>
+      <c r="T24" s="42"/>
+      <c r="U24" s="42"/>
+      <c r="V24" s="44"/>
+      <c r="W24" s="45" t="n">
         <f aca="false">SUM(N24:V24)</f>
         <v>0</v>
       </c>
-      <c r="X24" s="45"/>
-      <c r="Y24" s="46"/>
-      <c r="Z24" s="47" t="n">
+      <c r="X24" s="46"/>
+      <c r="Y24" s="47"/>
+      <c r="Z24" s="48" t="n">
         <f aca="false">W24+X24+Y24</f>
         <v>0</v>
       </c>
-      <c r="AA24" s="48"/>
+      <c r="AA24" s="49"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="33"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="35" t="n">
+      <c r="B25" s="34"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="36" t="n">
         <f aca="false">(I25-H25/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K25" s="50"/>
-      <c r="L25" s="51"/>
-      <c r="M25" s="52"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="40"/>
-      <c r="P25" s="40"/>
-      <c r="Q25" s="40"/>
-      <c r="R25" s="41"/>
-      <c r="S25" s="42"/>
-      <c r="T25" s="41"/>
-      <c r="U25" s="41"/>
-      <c r="V25" s="43"/>
-      <c r="W25" s="44" t="n">
+      <c r="K25" s="51"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="41"/>
+      <c r="R25" s="42"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="42"/>
+      <c r="U25" s="42"/>
+      <c r="V25" s="44"/>
+      <c r="W25" s="45" t="n">
         <f aca="false">SUM(N25:V25)</f>
         <v>0</v>
       </c>
-      <c r="X25" s="45"/>
-      <c r="Y25" s="46"/>
-      <c r="Z25" s="44" t="n">
+      <c r="X25" s="46"/>
+      <c r="Y25" s="47"/>
+      <c r="Z25" s="45" t="n">
         <f aca="false">SUM(V25:X25)</f>
         <v>0</v>
       </c>
-      <c r="AA25" s="48"/>
+      <c r="AA25" s="49"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="33"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="35" t="n">
+      <c r="B26" s="34"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="36" t="n">
         <f aca="false">(I26-H26/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K26" s="50"/>
-      <c r="L26" s="51"/>
-      <c r="M26" s="52"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="40"/>
-      <c r="R26" s="41"/>
-      <c r="S26" s="42"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="41"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="44" t="n">
+      <c r="K26" s="51"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="41"/>
+      <c r="R26" s="42"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="42"/>
+      <c r="U26" s="42"/>
+      <c r="V26" s="44"/>
+      <c r="W26" s="45" t="n">
         <f aca="false">SUM(N26:V26)</f>
         <v>0</v>
       </c>
-      <c r="X26" s="45"/>
-      <c r="Y26" s="46"/>
-      <c r="Z26" s="44" t="n">
+      <c r="X26" s="46"/>
+      <c r="Y26" s="47"/>
+      <c r="Z26" s="45" t="n">
         <f aca="false">SUM(V26:X26)</f>
         <v>0</v>
       </c>
-      <c r="AA26" s="48"/>
+      <c r="AA26" s="49"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="33"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="35" t="n">
+      <c r="B27" s="34"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="36" t="n">
         <f aca="false">(I27-H27/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K27" s="50"/>
-      <c r="L27" s="51"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
-      <c r="S27" s="42"/>
-      <c r="T27" s="41"/>
-      <c r="U27" s="41"/>
-      <c r="V27" s="43"/>
-      <c r="W27" s="44" t="n">
+      <c r="K27" s="51"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="42"/>
+      <c r="U27" s="42"/>
+      <c r="V27" s="44"/>
+      <c r="W27" s="45" t="n">
         <f aca="false">SUM(N27:V27)</f>
         <v>0</v>
       </c>
-      <c r="X27" s="45"/>
-      <c r="Y27" s="46"/>
-      <c r="Z27" s="44" t="n">
+      <c r="X27" s="46"/>
+      <c r="Y27" s="47"/>
+      <c r="Z27" s="45" t="n">
         <f aca="false">SUM(V27:X27)</f>
         <v>0</v>
       </c>
-      <c r="AA27" s="48"/>
+      <c r="AA27" s="49"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="33"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="35" t="n">
+      <c r="B28" s="34"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="36" t="n">
         <f aca="false">(I28-H28/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K28" s="50"/>
-      <c r="L28" s="51"/>
-      <c r="M28" s="52"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
-      <c r="S28" s="42"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="43"/>
-      <c r="W28" s="44" t="n">
+      <c r="K28" s="51"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="42"/>
+      <c r="U28" s="42"/>
+      <c r="V28" s="44"/>
+      <c r="W28" s="45" t="n">
         <f aca="false">SUM(N28:V28)</f>
         <v>0</v>
       </c>
-      <c r="X28" s="45"/>
-      <c r="Y28" s="46"/>
-      <c r="Z28" s="44" t="n">
+      <c r="X28" s="46"/>
+      <c r="Y28" s="47"/>
+      <c r="Z28" s="45" t="n">
         <f aca="false">SUM(V28:X28)</f>
         <v>0</v>
       </c>
-      <c r="AA28" s="48"/>
+      <c r="AA28" s="49"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="33"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="35" t="n">
+      <c r="B29" s="34"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="36" t="n">
         <f aca="false">(I29-H29/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K29" s="50"/>
-      <c r="L29" s="51"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
-      <c r="S29" s="42"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="41"/>
-      <c r="V29" s="43"/>
-      <c r="W29" s="44" t="n">
+      <c r="K29" s="51"/>
+      <c r="L29" s="52"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
+      <c r="S29" s="43"/>
+      <c r="T29" s="42"/>
+      <c r="U29" s="42"/>
+      <c r="V29" s="44"/>
+      <c r="W29" s="45" t="n">
         <f aca="false">SUM(N29:V29)</f>
         <v>0</v>
       </c>
-      <c r="X29" s="45"/>
-      <c r="Y29" s="46"/>
-      <c r="Z29" s="44" t="n">
+      <c r="X29" s="46"/>
+      <c r="Y29" s="47"/>
+      <c r="Z29" s="45" t="n">
         <f aca="false">SUM(V29:X29)</f>
         <v>0</v>
       </c>
-      <c r="AA29" s="48"/>
+      <c r="AA29" s="49"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="33"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="35" t="n">
+      <c r="B30" s="34"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="36" t="n">
         <f aca="false">(I30-H30/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K30" s="50"/>
-      <c r="L30" s="51"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="41"/>
-      <c r="V30" s="43"/>
-      <c r="W30" s="44" t="n">
+      <c r="K30" s="51"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="42"/>
+      <c r="U30" s="42"/>
+      <c r="V30" s="44"/>
+      <c r="W30" s="45" t="n">
         <f aca="false">SUM(N30:V30)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="45"/>
-      <c r="Y30" s="46"/>
-      <c r="Z30" s="44" t="n">
+      <c r="X30" s="46"/>
+      <c r="Y30" s="47"/>
+      <c r="Z30" s="45" t="n">
         <f aca="false">SUM(V30:X30)</f>
         <v>0</v>
       </c>
-      <c r="AA30" s="48"/>
+      <c r="AA30" s="49"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="33"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="35" t="n">
+      <c r="B31" s="34"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="36" t="n">
         <f aca="false">(I31-H31/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K31" s="50"/>
-      <c r="L31" s="51"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
-      <c r="S31" s="42"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="41"/>
-      <c r="V31" s="43"/>
-      <c r="W31" s="44" t="n">
+      <c r="K31" s="51"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
+      <c r="S31" s="43"/>
+      <c r="T31" s="42"/>
+      <c r="U31" s="42"/>
+      <c r="V31" s="44"/>
+      <c r="W31" s="45" t="n">
         <f aca="false">SUM(N31:V31)</f>
         <v>0</v>
       </c>
-      <c r="X31" s="45"/>
-      <c r="Y31" s="46"/>
-      <c r="Z31" s="44" t="n">
+      <c r="X31" s="46"/>
+      <c r="Y31" s="47"/>
+      <c r="Z31" s="45" t="n">
         <f aca="false">SUM(V31:X31)</f>
         <v>0</v>
       </c>
-      <c r="AA31" s="48"/>
+      <c r="AA31" s="49"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="33"/>
-      <c r="B32" s="57"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="58"/>
       <c r="D32" s="58"/>
       <c r="E32" s="58"/>
@@ -2959,34 +2959,34 @@
       <c r="G32" s="58"/>
       <c r="H32" s="58"/>
       <c r="I32" s="58"/>
-      <c r="J32" s="35"/>
+      <c r="J32" s="36"/>
       <c r="K32" s="58"/>
-      <c r="L32" s="51"/>
-      <c r="M32" s="52"/>
-      <c r="N32" s="39"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
-      <c r="S32" s="42"/>
-      <c r="T32" s="41"/>
-      <c r="U32" s="41"/>
-      <c r="V32" s="43"/>
-      <c r="W32" s="44" t="n">
+      <c r="L32" s="52"/>
+      <c r="M32" s="53"/>
+      <c r="N32" s="40"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
+      <c r="S32" s="43"/>
+      <c r="T32" s="42"/>
+      <c r="U32" s="42"/>
+      <c r="V32" s="44"/>
+      <c r="W32" s="45" t="n">
         <f aca="false">SUM(N32:V32)</f>
         <v>0</v>
       </c>
-      <c r="X32" s="45"/>
-      <c r="Y32" s="46"/>
-      <c r="Z32" s="44" t="n">
+      <c r="X32" s="46"/>
+      <c r="Y32" s="47"/>
+      <c r="Z32" s="45" t="n">
         <f aca="false">SUM(V32:X32)</f>
         <v>0</v>
       </c>
-      <c r="AA32" s="48"/>
+      <c r="AA32" s="49"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="33"/>
-      <c r="B33" s="57"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="58"/>
       <c r="D33" s="58"/>
       <c r="E33" s="58"/>
@@ -2994,34 +2994,34 @@
       <c r="G33" s="58"/>
       <c r="H33" s="58"/>
       <c r="I33" s="58"/>
-      <c r="J33" s="35"/>
+      <c r="J33" s="36"/>
       <c r="K33" s="58"/>
-      <c r="L33" s="51"/>
-      <c r="M33" s="52"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
-      <c r="S33" s="42"/>
-      <c r="T33" s="41"/>
-      <c r="U33" s="41"/>
-      <c r="V33" s="43"/>
-      <c r="W33" s="44" t="n">
+      <c r="L33" s="52"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
+      <c r="S33" s="43"/>
+      <c r="T33" s="42"/>
+      <c r="U33" s="42"/>
+      <c r="V33" s="44"/>
+      <c r="W33" s="45" t="n">
         <f aca="false">SUM(N33:V33)</f>
         <v>0</v>
       </c>
-      <c r="X33" s="45"/>
-      <c r="Y33" s="46"/>
-      <c r="Z33" s="44" t="n">
+      <c r="X33" s="46"/>
+      <c r="Y33" s="47"/>
+      <c r="Z33" s="45" t="n">
         <f aca="false">SUM(V33:X33)</f>
         <v>0</v>
       </c>
-      <c r="AA33" s="48"/>
+      <c r="AA33" s="49"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="33"/>
-      <c r="B34" s="57"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="58"/>
       <c r="D34" s="58"/>
       <c r="E34" s="58"/>
@@ -3029,34 +3029,34 @@
       <c r="G34" s="58"/>
       <c r="H34" s="58"/>
       <c r="I34" s="58"/>
-      <c r="J34" s="35"/>
+      <c r="J34" s="36"/>
       <c r="K34" s="58"/>
-      <c r="L34" s="51"/>
-      <c r="M34" s="52"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
-      <c r="S34" s="42"/>
-      <c r="T34" s="41"/>
-      <c r="U34" s="41"/>
-      <c r="V34" s="43"/>
-      <c r="W34" s="44" t="n">
+      <c r="L34" s="52"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="40"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
+      <c r="S34" s="43"/>
+      <c r="T34" s="42"/>
+      <c r="U34" s="42"/>
+      <c r="V34" s="44"/>
+      <c r="W34" s="45" t="n">
         <f aca="false">SUM(N34:V34)</f>
         <v>0</v>
       </c>
-      <c r="X34" s="45"/>
-      <c r="Y34" s="46"/>
-      <c r="Z34" s="44" t="n">
+      <c r="X34" s="46"/>
+      <c r="Y34" s="47"/>
+      <c r="Z34" s="45" t="n">
         <f aca="false">SUM(V34:X34)</f>
         <v>0</v>
       </c>
-      <c r="AA34" s="48"/>
+      <c r="AA34" s="49"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="33"/>
-      <c r="B35" s="57"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="58"/>
       <c r="D35" s="58"/>
       <c r="E35" s="58"/>
@@ -3064,34 +3064,34 @@
       <c r="G35" s="58"/>
       <c r="H35" s="58"/>
       <c r="I35" s="58"/>
-      <c r="J35" s="35"/>
+      <c r="J35" s="36"/>
       <c r="K35" s="58"/>
-      <c r="L35" s="51"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
-      <c r="S35" s="42"/>
-      <c r="T35" s="41"/>
-      <c r="U35" s="41"/>
-      <c r="V35" s="43"/>
-      <c r="W35" s="44" t="n">
+      <c r="L35" s="52"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="40"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
+      <c r="S35" s="43"/>
+      <c r="T35" s="42"/>
+      <c r="U35" s="42"/>
+      <c r="V35" s="44"/>
+      <c r="W35" s="45" t="n">
         <f aca="false">SUM(N35:V35)</f>
         <v>0</v>
       </c>
-      <c r="X35" s="45"/>
-      <c r="Y35" s="46"/>
-      <c r="Z35" s="44" t="n">
+      <c r="X35" s="46"/>
+      <c r="Y35" s="47"/>
+      <c r="Z35" s="45" t="n">
         <f aca="false">SUM(V35:X35)</f>
         <v>0</v>
       </c>
-      <c r="AA35" s="48"/>
+      <c r="AA35" s="49"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="33"/>
-      <c r="B36" s="57"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="58"/>
       <c r="D36" s="58"/>
       <c r="E36" s="58"/>
@@ -3099,28 +3099,28 @@
       <c r="G36" s="58"/>
       <c r="H36" s="58"/>
       <c r="I36" s="58"/>
-      <c r="J36" s="35"/>
+      <c r="J36" s="36"/>
       <c r="K36" s="58"/>
-      <c r="L36" s="51"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="42"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="43"/>
-      <c r="W36" s="44"/>
-      <c r="X36" s="45"/>
-      <c r="Y36" s="46"/>
-      <c r="Z36" s="44"/>
-      <c r="AA36" s="48"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="53"/>
+      <c r="N36" s="40"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
+      <c r="S36" s="43"/>
+      <c r="T36" s="42"/>
+      <c r="U36" s="42"/>
+      <c r="V36" s="44"/>
+      <c r="W36" s="45"/>
+      <c r="X36" s="46"/>
+      <c r="Y36" s="47"/>
+      <c r="Z36" s="45"/>
+      <c r="AA36" s="49"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="33"/>
-      <c r="B37" s="57"/>
+      <c r="B37" s="34"/>
       <c r="C37" s="58"/>
       <c r="D37" s="58"/>
       <c r="E37" s="58"/>
@@ -3128,28 +3128,28 @@
       <c r="G37" s="58"/>
       <c r="H37" s="58"/>
       <c r="I37" s="58"/>
-      <c r="J37" s="35"/>
+      <c r="J37" s="36"/>
       <c r="K37" s="58"/>
-      <c r="L37" s="51"/>
-      <c r="M37" s="52"/>
-      <c r="N37" s="39"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
-      <c r="S37" s="42"/>
-      <c r="T37" s="41"/>
-      <c r="U37" s="41"/>
-      <c r="V37" s="43"/>
-      <c r="W37" s="44"/>
-      <c r="X37" s="45"/>
-      <c r="Y37" s="46"/>
-      <c r="Z37" s="44"/>
-      <c r="AA37" s="48"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="53"/>
+      <c r="N37" s="40"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
+      <c r="S37" s="43"/>
+      <c r="T37" s="42"/>
+      <c r="U37" s="42"/>
+      <c r="V37" s="44"/>
+      <c r="W37" s="45"/>
+      <c r="X37" s="46"/>
+      <c r="Y37" s="47"/>
+      <c r="Z37" s="45"/>
+      <c r="AA37" s="49"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="33"/>
-      <c r="B38" s="57"/>
+      <c r="B38" s="34"/>
       <c r="C38" s="58"/>
       <c r="D38" s="58"/>
       <c r="E38" s="58"/>
@@ -3157,28 +3157,28 @@
       <c r="G38" s="58"/>
       <c r="H38" s="58"/>
       <c r="I38" s="58"/>
-      <c r="J38" s="35"/>
+      <c r="J38" s="36"/>
       <c r="K38" s="58"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="52"/>
-      <c r="N38" s="39"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
-      <c r="S38" s="42"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="41"/>
-      <c r="V38" s="43"/>
-      <c r="W38" s="44"/>
-      <c r="X38" s="45"/>
-      <c r="Y38" s="46"/>
-      <c r="Z38" s="44"/>
-      <c r="AA38" s="48"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="53"/>
+      <c r="N38" s="40"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
+      <c r="S38" s="43"/>
+      <c r="T38" s="42"/>
+      <c r="U38" s="42"/>
+      <c r="V38" s="44"/>
+      <c r="W38" s="45"/>
+      <c r="X38" s="46"/>
+      <c r="Y38" s="47"/>
+      <c r="Z38" s="45"/>
+      <c r="AA38" s="49"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="33"/>
-      <c r="B39" s="57"/>
+      <c r="B39" s="34"/>
       <c r="C39" s="58"/>
       <c r="D39" s="58"/>
       <c r="E39" s="58"/>
@@ -3186,28 +3186,28 @@
       <c r="G39" s="58"/>
       <c r="H39" s="58"/>
       <c r="I39" s="58"/>
-      <c r="J39" s="35"/>
+      <c r="J39" s="36"/>
       <c r="K39" s="58"/>
-      <c r="L39" s="51"/>
-      <c r="M39" s="52"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
-      <c r="S39" s="42"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="41"/>
-      <c r="V39" s="43"/>
-      <c r="W39" s="44"/>
-      <c r="X39" s="45"/>
-      <c r="Y39" s="46"/>
-      <c r="Z39" s="44"/>
-      <c r="AA39" s="48"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="53"/>
+      <c r="N39" s="40"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
+      <c r="S39" s="43"/>
+      <c r="T39" s="42"/>
+      <c r="U39" s="42"/>
+      <c r="V39" s="44"/>
+      <c r="W39" s="45"/>
+      <c r="X39" s="46"/>
+      <c r="Y39" s="47"/>
+      <c r="Z39" s="45"/>
+      <c r="AA39" s="49"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="33"/>
-      <c r="B40" s="57"/>
+      <c r="B40" s="34"/>
       <c r="C40" s="58"/>
       <c r="D40" s="58"/>
       <c r="E40" s="58"/>
@@ -3215,28 +3215,28 @@
       <c r="G40" s="58"/>
       <c r="H40" s="58"/>
       <c r="I40" s="58"/>
-      <c r="J40" s="35"/>
+      <c r="J40" s="36"/>
       <c r="K40" s="58"/>
-      <c r="L40" s="51"/>
-      <c r="M40" s="52"/>
-      <c r="N40" s="39"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
-      <c r="S40" s="42"/>
-      <c r="T40" s="41"/>
-      <c r="U40" s="41"/>
-      <c r="V40" s="43"/>
-      <c r="W40" s="44"/>
-      <c r="X40" s="45"/>
-      <c r="Y40" s="46"/>
-      <c r="Z40" s="44"/>
-      <c r="AA40" s="48"/>
+      <c r="L40" s="52"/>
+      <c r="M40" s="53"/>
+      <c r="N40" s="40"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="42"/>
+      <c r="U40" s="42"/>
+      <c r="V40" s="44"/>
+      <c r="W40" s="45"/>
+      <c r="X40" s="46"/>
+      <c r="Y40" s="47"/>
+      <c r="Z40" s="45"/>
+      <c r="AA40" s="49"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="33"/>
-      <c r="B41" s="57"/>
+      <c r="B41" s="34"/>
       <c r="C41" s="58"/>
       <c r="D41" s="58"/>
       <c r="E41" s="58"/>
@@ -3244,28 +3244,28 @@
       <c r="G41" s="58"/>
       <c r="H41" s="58"/>
       <c r="I41" s="58"/>
-      <c r="J41" s="35"/>
+      <c r="J41" s="36"/>
       <c r="K41" s="58"/>
-      <c r="L41" s="51"/>
-      <c r="M41" s="52"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
-      <c r="S41" s="42"/>
-      <c r="T41" s="41"/>
-      <c r="U41" s="41"/>
-      <c r="V41" s="43"/>
-      <c r="W41" s="44"/>
-      <c r="X41" s="45"/>
-      <c r="Y41" s="46"/>
-      <c r="Z41" s="44"/>
-      <c r="AA41" s="48"/>
+      <c r="L41" s="52"/>
+      <c r="M41" s="53"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
+      <c r="S41" s="43"/>
+      <c r="T41" s="42"/>
+      <c r="U41" s="42"/>
+      <c r="V41" s="44"/>
+      <c r="W41" s="45"/>
+      <c r="X41" s="46"/>
+      <c r="Y41" s="47"/>
+      <c r="Z41" s="45"/>
+      <c r="AA41" s="49"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="33"/>
-      <c r="B42" s="57"/>
+      <c r="B42" s="34"/>
       <c r="C42" s="58"/>
       <c r="D42" s="58"/>
       <c r="E42" s="58"/>
@@ -3273,28 +3273,28 @@
       <c r="G42" s="58"/>
       <c r="H42" s="58"/>
       <c r="I42" s="58"/>
-      <c r="J42" s="35"/>
+      <c r="J42" s="36"/>
       <c r="K42" s="58"/>
-      <c r="L42" s="51"/>
-      <c r="M42" s="52"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
-      <c r="S42" s="42"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="41"/>
-      <c r="V42" s="43"/>
-      <c r="W42" s="44"/>
-      <c r="X42" s="45"/>
-      <c r="Y42" s="46"/>
-      <c r="Z42" s="44"/>
-      <c r="AA42" s="48"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="53"/>
+      <c r="N42" s="40"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
+      <c r="S42" s="43"/>
+      <c r="T42" s="42"/>
+      <c r="U42" s="42"/>
+      <c r="V42" s="44"/>
+      <c r="W42" s="45"/>
+      <c r="X42" s="46"/>
+      <c r="Y42" s="47"/>
+      <c r="Z42" s="45"/>
+      <c r="AA42" s="49"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="33"/>
-      <c r="B43" s="57"/>
+      <c r="B43" s="34"/>
       <c r="C43" s="58"/>
       <c r="D43" s="58"/>
       <c r="E43" s="58"/>
@@ -3302,28 +3302,28 @@
       <c r="G43" s="58"/>
       <c r="H43" s="58"/>
       <c r="I43" s="58"/>
-      <c r="J43" s="35"/>
+      <c r="J43" s="36"/>
       <c r="K43" s="58"/>
-      <c r="L43" s="51"/>
-      <c r="M43" s="52"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
-      <c r="S43" s="42"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="41"/>
-      <c r="V43" s="43"/>
-      <c r="W43" s="44"/>
-      <c r="X43" s="45"/>
-      <c r="Y43" s="46"/>
-      <c r="Z43" s="44"/>
-      <c r="AA43" s="48"/>
+      <c r="L43" s="52"/>
+      <c r="M43" s="53"/>
+      <c r="N43" s="40"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="43"/>
+      <c r="T43" s="42"/>
+      <c r="U43" s="42"/>
+      <c r="V43" s="44"/>
+      <c r="W43" s="45"/>
+      <c r="X43" s="46"/>
+      <c r="Y43" s="47"/>
+      <c r="Z43" s="45"/>
+      <c r="AA43" s="49"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="33"/>
-      <c r="B44" s="57"/>
+      <c r="B44" s="34"/>
       <c r="C44" s="58"/>
       <c r="D44" s="58"/>
       <c r="E44" s="58"/>
@@ -3331,28 +3331,28 @@
       <c r="G44" s="58"/>
       <c r="H44" s="58"/>
       <c r="I44" s="58"/>
-      <c r="J44" s="35"/>
+      <c r="J44" s="36"/>
       <c r="K44" s="58"/>
-      <c r="L44" s="51"/>
-      <c r="M44" s="52"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
-      <c r="S44" s="42"/>
-      <c r="T44" s="41"/>
-      <c r="U44" s="41"/>
-      <c r="V44" s="43"/>
-      <c r="W44" s="44"/>
-      <c r="X44" s="45"/>
-      <c r="Y44" s="46"/>
-      <c r="Z44" s="44"/>
-      <c r="AA44" s="48"/>
+      <c r="L44" s="52"/>
+      <c r="M44" s="53"/>
+      <c r="N44" s="40"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="43"/>
+      <c r="T44" s="42"/>
+      <c r="U44" s="42"/>
+      <c r="V44" s="44"/>
+      <c r="W44" s="45"/>
+      <c r="X44" s="46"/>
+      <c r="Y44" s="47"/>
+      <c r="Z44" s="45"/>
+      <c r="AA44" s="49"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="33"/>
-      <c r="B45" s="57"/>
+      <c r="B45" s="34"/>
       <c r="C45" s="58"/>
       <c r="D45" s="58"/>
       <c r="E45" s="58"/>
@@ -3360,34 +3360,34 @@
       <c r="G45" s="58"/>
       <c r="H45" s="58"/>
       <c r="I45" s="58"/>
-      <c r="J45" s="35"/>
+      <c r="J45" s="36"/>
       <c r="K45" s="58"/>
-      <c r="L45" s="51"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="40"/>
-      <c r="P45" s="40"/>
-      <c r="Q45" s="40"/>
-      <c r="R45" s="41"/>
-      <c r="S45" s="42"/>
-      <c r="T45" s="41"/>
-      <c r="U45" s="41"/>
-      <c r="V45" s="43"/>
-      <c r="W45" s="44" t="n">
+      <c r="L45" s="52"/>
+      <c r="M45" s="53"/>
+      <c r="N45" s="40"/>
+      <c r="O45" s="41"/>
+      <c r="P45" s="41"/>
+      <c r="Q45" s="41"/>
+      <c r="R45" s="42"/>
+      <c r="S45" s="43"/>
+      <c r="T45" s="42"/>
+      <c r="U45" s="42"/>
+      <c r="V45" s="44"/>
+      <c r="W45" s="45" t="n">
         <f aca="false">SUM(N45:V45)</f>
         <v>0</v>
       </c>
-      <c r="X45" s="45"/>
-      <c r="Y45" s="46"/>
-      <c r="Z45" s="44" t="n">
+      <c r="X45" s="46"/>
+      <c r="Y45" s="47"/>
+      <c r="Z45" s="45" t="n">
         <f aca="false">SUM(V45:X45)</f>
         <v>0</v>
       </c>
-      <c r="AA45" s="48"/>
+      <c r="AA45" s="49"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="33"/>
-      <c r="B46" s="57"/>
+      <c r="B46" s="34"/>
       <c r="C46" s="58"/>
       <c r="D46" s="58"/>
       <c r="E46" s="58"/>
@@ -3395,34 +3395,34 @@
       <c r="G46" s="58"/>
       <c r="H46" s="58"/>
       <c r="I46" s="58"/>
-      <c r="J46" s="35"/>
+      <c r="J46" s="36"/>
       <c r="K46" s="58"/>
-      <c r="L46" s="51"/>
-      <c r="M46" s="52"/>
-      <c r="N46" s="39"/>
-      <c r="O46" s="40"/>
-      <c r="P46" s="40"/>
-      <c r="Q46" s="40"/>
-      <c r="R46" s="41"/>
-      <c r="S46" s="42"/>
-      <c r="T46" s="41"/>
-      <c r="U46" s="41"/>
-      <c r="V46" s="43"/>
-      <c r="W46" s="44" t="n">
+      <c r="L46" s="52"/>
+      <c r="M46" s="53"/>
+      <c r="N46" s="40"/>
+      <c r="O46" s="41"/>
+      <c r="P46" s="41"/>
+      <c r="Q46" s="41"/>
+      <c r="R46" s="42"/>
+      <c r="S46" s="43"/>
+      <c r="T46" s="42"/>
+      <c r="U46" s="42"/>
+      <c r="V46" s="44"/>
+      <c r="W46" s="45" t="n">
         <f aca="false">SUM(N46:V46)</f>
         <v>0</v>
       </c>
-      <c r="X46" s="45"/>
-      <c r="Y46" s="46"/>
-      <c r="Z46" s="44" t="n">
+      <c r="X46" s="46"/>
+      <c r="Y46" s="47"/>
+      <c r="Z46" s="45" t="n">
         <f aca="false">SUM(V46:X46)</f>
         <v>0</v>
       </c>
-      <c r="AA46" s="48"/>
+      <c r="AA46" s="49"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="33"/>
-      <c r="B47" s="57"/>
+      <c r="B47" s="34"/>
       <c r="C47" s="58"/>
       <c r="D47" s="58"/>
       <c r="E47" s="58"/>
@@ -3430,7 +3430,7 @@
       <c r="G47" s="58"/>
       <c r="H47" s="58"/>
       <c r="I47" s="58"/>
-      <c r="J47" s="35"/>
+      <c r="J47" s="36"/>
       <c r="K47" s="58"/>
       <c r="L47" s="60"/>
       <c r="M47" s="61"/>
@@ -3451,7 +3451,7 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="33"/>
-      <c r="B48" s="57"/>
+      <c r="B48" s="34"/>
       <c r="C48" s="58"/>
       <c r="D48" s="58"/>
       <c r="E48" s="58"/>
@@ -3459,7 +3459,7 @@
       <c r="G48" s="58"/>
       <c r="H48" s="58"/>
       <c r="I48" s="58"/>
-      <c r="J48" s="35"/>
+      <c r="J48" s="36"/>
       <c r="K48" s="58"/>
       <c r="L48" s="60"/>
       <c r="M48" s="61"/>
@@ -3480,19 +3480,19 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="33"/>
-      <c r="B49" s="49"/>
-      <c r="C49" s="49"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="49"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="49"/>
-      <c r="J49" s="35" t="n">
+      <c r="B49" s="34"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="50"/>
+      <c r="H49" s="50"/>
+      <c r="I49" s="50"/>
+      <c r="J49" s="36" t="n">
         <f aca="false">(I49-H49/8.5)*1.33</f>
         <v>0</v>
       </c>
-      <c r="K49" s="50"/>
+      <c r="K49" s="51"/>
       <c r="L49" s="60"/>
       <c r="M49" s="61"/>
       <c r="N49" s="71"/>
@@ -3777,7 +3777,7 @@
       <c r="AA59" s="95"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="N60" s="35" t="n">
+      <c r="N60" s="36" t="n">
         <f aca="false">SUM(N17:N59)</f>
         <v>0</v>
       </c>

--- a/template.xlsx
+++ b/template.xlsx
@@ -1246,7 +1246,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2048,7 +2048,7 @@
       <c r="H8" s="50"/>
       <c r="I8" s="50"/>
       <c r="J8" s="36" t="n">
-        <f aca="false">(I8-H8/8.5)*1.33</f>
+        <f aca="false">(I8-H8)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K8" s="51"/>
@@ -2086,7 +2086,7 @@
       <c r="H9" s="50"/>
       <c r="I9" s="50"/>
       <c r="J9" s="36" t="n">
-        <f aca="false">(I9-H9/8.5)*1.33</f>
+        <f aca="false">(I9-H9)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K9" s="51"/>
@@ -2124,7 +2124,7 @@
       <c r="H10" s="50"/>
       <c r="I10" s="50"/>
       <c r="J10" s="36" t="n">
-        <f aca="false">(I10-H10/8.5)*1.33</f>
+        <f aca="false">(I10-H10)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K10" s="51"/>
@@ -2162,7 +2162,7 @@
       <c r="H11" s="50"/>
       <c r="I11" s="50"/>
       <c r="J11" s="36" t="n">
-        <f aca="false">(I11-H11/8.5)*1.33</f>
+        <f aca="false">(I11-H11)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K11" s="51"/>
@@ -2200,7 +2200,7 @@
       <c r="H12" s="50"/>
       <c r="I12" s="50"/>
       <c r="J12" s="36" t="n">
-        <f aca="false">(I12-H12/8.5)*1.33</f>
+        <f aca="false">(I12-H12)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K12" s="51"/>
@@ -2238,7 +2238,7 @@
       <c r="H13" s="50"/>
       <c r="I13" s="50"/>
       <c r="J13" s="36" t="n">
-        <f aca="false">(I13-H13/8.5)*1.33</f>
+        <f aca="false">(I13-H13)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K13" s="51"/>
@@ -2276,7 +2276,7 @@
       <c r="H14" s="50"/>
       <c r="I14" s="50"/>
       <c r="J14" s="36" t="n">
-        <f aca="false">(I14-H14/8.5)*1.33</f>
+        <f aca="false">(I14-H14)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K14" s="51"/>
@@ -2314,7 +2314,7 @@
       <c r="H15" s="50"/>
       <c r="I15" s="50"/>
       <c r="J15" s="36" t="n">
-        <f aca="false">(I15-H15/8.5)*1.33</f>
+        <f aca="false">(I15-H15)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K15" s="51"/>
@@ -2352,7 +2352,7 @@
       <c r="H16" s="50"/>
       <c r="I16" s="50"/>
       <c r="J16" s="36" t="n">
-        <f aca="false">(I16-H16/8.5)*1.33</f>
+        <f aca="false">(I16-H16)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K16" s="51"/>
@@ -2390,7 +2390,7 @@
       <c r="H17" s="50"/>
       <c r="I17" s="50"/>
       <c r="J17" s="36" t="n">
-        <f aca="false">(I17-H17/8.5)*1.33</f>
+        <f aca="false">(I17-H17)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K17" s="51"/>
@@ -2428,7 +2428,7 @@
       <c r="H18" s="50"/>
       <c r="I18" s="50"/>
       <c r="J18" s="36" t="n">
-        <f aca="false">(I18-H18/8.5)*1.33</f>
+        <f aca="false">(I18-H18)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K18" s="51"/>
@@ -2466,7 +2466,7 @@
       <c r="H19" s="50"/>
       <c r="I19" s="50"/>
       <c r="J19" s="36" t="n">
-        <f aca="false">(I19-H19/8.5)*1.33</f>
+        <f aca="false">(I19-H19)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K19" s="51"/>
@@ -2504,7 +2504,7 @@
       <c r="H20" s="50"/>
       <c r="I20" s="50"/>
       <c r="J20" s="36" t="n">
-        <f aca="false">(I20-H20/8.5)*1.33</f>
+        <f aca="false">(I20-H20)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K20" s="51"/>
@@ -2542,7 +2542,7 @@
       <c r="H21" s="50"/>
       <c r="I21" s="50"/>
       <c r="J21" s="36" t="n">
-        <f aca="false">(I21-H21/8.5)*1.33</f>
+        <f aca="false">(I21-H21)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K21" s="51"/>
@@ -2580,7 +2580,7 @@
       <c r="H22" s="50"/>
       <c r="I22" s="50"/>
       <c r="J22" s="36" t="n">
-        <f aca="false">(I22-H22/8.5)*1.33</f>
+        <f aca="false">(I22-H22)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K22" s="51"/>
@@ -2618,7 +2618,7 @@
       <c r="H23" s="50"/>
       <c r="I23" s="50"/>
       <c r="J23" s="36" t="n">
-        <f aca="false">(I23-H23/8.5)*1.33</f>
+        <f aca="false">(I23-H23)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K23" s="51"/>
@@ -2656,7 +2656,7 @@
       <c r="H24" s="50"/>
       <c r="I24" s="50"/>
       <c r="J24" s="36" t="n">
-        <f aca="false">(I24-H24/8.5)*1.33</f>
+        <f aca="false">(I24-H24)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K24" s="51"/>
@@ -2694,7 +2694,7 @@
       <c r="H25" s="50"/>
       <c r="I25" s="50"/>
       <c r="J25" s="36" t="n">
-        <f aca="false">(I25-H25/8.5)*1.33</f>
+        <f aca="false">(I25-H25)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K25" s="51"/>
@@ -2732,7 +2732,7 @@
       <c r="H26" s="50"/>
       <c r="I26" s="50"/>
       <c r="J26" s="36" t="n">
-        <f aca="false">(I26-H26/8.5)*1.33</f>
+        <f aca="false">(I26-H26)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K26" s="51"/>
@@ -2770,7 +2770,7 @@
       <c r="H27" s="50"/>
       <c r="I27" s="50"/>
       <c r="J27" s="36" t="n">
-        <f aca="false">(I27-H27/8.5)*1.33</f>
+        <f aca="false">(I27-H27)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K27" s="51"/>
@@ -2808,7 +2808,7 @@
       <c r="H28" s="50"/>
       <c r="I28" s="50"/>
       <c r="J28" s="36" t="n">
-        <f aca="false">(I28-H28/8.5)*1.33</f>
+        <f aca="false">(I28-H28)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K28" s="51"/>
@@ -2846,7 +2846,7 @@
       <c r="H29" s="50"/>
       <c r="I29" s="50"/>
       <c r="J29" s="36" t="n">
-        <f aca="false">(I29-H29/8.5)*1.33</f>
+        <f aca="false">(I29-H29)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K29" s="51"/>
@@ -2884,7 +2884,7 @@
       <c r="H30" s="50"/>
       <c r="I30" s="50"/>
       <c r="J30" s="36" t="n">
-        <f aca="false">(I30-H30/8.5)*1.33</f>
+        <f aca="false">(I30-H30)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K30" s="51"/>
@@ -2922,7 +2922,7 @@
       <c r="H31" s="50"/>
       <c r="I31" s="50"/>
       <c r="J31" s="36" t="n">
-        <f aca="false">(I31-H31/8.5)*1.33</f>
+        <f aca="false">(I31-H31)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K31" s="51"/>
@@ -3489,7 +3489,7 @@
       <c r="H49" s="50"/>
       <c r="I49" s="50"/>
       <c r="J49" s="36" t="n">
-        <f aca="false">(I49-H49/8.5)*1.33</f>
+        <f aca="false">(I49-H49)/8.5*1.33</f>
         <v>0</v>
       </c>
       <c r="K49" s="51"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -2010,7 +2010,7 @@
       <c r="H7" s="35"/>
       <c r="I7" s="35"/>
       <c r="J7" s="36" t="n">
-        <f aca="false">(I7-H7)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I7-H7)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K7" s="37"/>
@@ -2048,7 +2048,7 @@
       <c r="H8" s="50"/>
       <c r="I8" s="50"/>
       <c r="J8" s="36" t="n">
-        <f aca="false">(I8-H8)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I8-H8)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K8" s="51"/>
@@ -2086,7 +2086,7 @@
       <c r="H9" s="50"/>
       <c r="I9" s="50"/>
       <c r="J9" s="36" t="n">
-        <f aca="false">(I9-H9)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I9-H9)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K9" s="51"/>
@@ -2124,7 +2124,7 @@
       <c r="H10" s="50"/>
       <c r="I10" s="50"/>
       <c r="J10" s="36" t="n">
-        <f aca="false">(I10-H10)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I10-H10)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K10" s="51"/>
@@ -2162,7 +2162,7 @@
       <c r="H11" s="50"/>
       <c r="I11" s="50"/>
       <c r="J11" s="36" t="n">
-        <f aca="false">(I11-H11)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I11-H11)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K11" s="51"/>
@@ -2200,7 +2200,7 @@
       <c r="H12" s="50"/>
       <c r="I12" s="50"/>
       <c r="J12" s="36" t="n">
-        <f aca="false">(I12-H12)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I12-H12)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K12" s="51"/>
@@ -2238,7 +2238,7 @@
       <c r="H13" s="50"/>
       <c r="I13" s="50"/>
       <c r="J13" s="36" t="n">
-        <f aca="false">(I13-H13)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I13-H13)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K13" s="51"/>
@@ -2276,7 +2276,7 @@
       <c r="H14" s="50"/>
       <c r="I14" s="50"/>
       <c r="J14" s="36" t="n">
-        <f aca="false">(I14-H14)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I14-H14)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K14" s="51"/>
@@ -2314,7 +2314,7 @@
       <c r="H15" s="50"/>
       <c r="I15" s="50"/>
       <c r="J15" s="36" t="n">
-        <f aca="false">(I15-H15)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I15-H15)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K15" s="51"/>
@@ -2352,7 +2352,7 @@
       <c r="H16" s="50"/>
       <c r="I16" s="50"/>
       <c r="J16" s="36" t="n">
-        <f aca="false">(I16-H16)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I16-H16)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K16" s="51"/>
@@ -2390,7 +2390,7 @@
       <c r="H17" s="50"/>
       <c r="I17" s="50"/>
       <c r="J17" s="36" t="n">
-        <f aca="false">(I17-H17)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I17-H17)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K17" s="51"/>
@@ -2428,7 +2428,7 @@
       <c r="H18" s="50"/>
       <c r="I18" s="50"/>
       <c r="J18" s="36" t="n">
-        <f aca="false">(I18-H18)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I18-H18)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K18" s="51"/>
@@ -2466,7 +2466,7 @@
       <c r="H19" s="50"/>
       <c r="I19" s="50"/>
       <c r="J19" s="36" t="n">
-        <f aca="false">(I19-H19)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I19-H19)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K19" s="51"/>
@@ -2504,7 +2504,7 @@
       <c r="H20" s="50"/>
       <c r="I20" s="50"/>
       <c r="J20" s="36" t="n">
-        <f aca="false">(I20-H20)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I20-H20)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K20" s="51"/>
@@ -2542,7 +2542,7 @@
       <c r="H21" s="50"/>
       <c r="I21" s="50"/>
       <c r="J21" s="36" t="n">
-        <f aca="false">(I21-H21)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I21-H21)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K21" s="51"/>
@@ -2580,7 +2580,7 @@
       <c r="H22" s="50"/>
       <c r="I22" s="50"/>
       <c r="J22" s="36" t="n">
-        <f aca="false">(I22-H22)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I22-H22)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K22" s="51"/>
@@ -2618,7 +2618,7 @@
       <c r="H23" s="50"/>
       <c r="I23" s="50"/>
       <c r="J23" s="36" t="n">
-        <f aca="false">(I23-H23)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I23-H23)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K23" s="51"/>
@@ -2656,7 +2656,7 @@
       <c r="H24" s="50"/>
       <c r="I24" s="50"/>
       <c r="J24" s="36" t="n">
-        <f aca="false">(I24-H24)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I24-H24)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K24" s="51"/>
@@ -2694,7 +2694,7 @@
       <c r="H25" s="50"/>
       <c r="I25" s="50"/>
       <c r="J25" s="36" t="n">
-        <f aca="false">(I25-H25)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I25-H25)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K25" s="51"/>
@@ -2732,7 +2732,7 @@
       <c r="H26" s="50"/>
       <c r="I26" s="50"/>
       <c r="J26" s="36" t="n">
-        <f aca="false">(I26-H26)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I26-H26)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K26" s="51"/>
@@ -2770,7 +2770,7 @@
       <c r="H27" s="50"/>
       <c r="I27" s="50"/>
       <c r="J27" s="36" t="n">
-        <f aca="false">(I27-H27)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I27-H27)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K27" s="51"/>
@@ -2808,7 +2808,7 @@
       <c r="H28" s="50"/>
       <c r="I28" s="50"/>
       <c r="J28" s="36" t="n">
-        <f aca="false">(I28-H28)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I28-H28)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K28" s="51"/>
@@ -2846,7 +2846,7 @@
       <c r="H29" s="50"/>
       <c r="I29" s="50"/>
       <c r="J29" s="36" t="n">
-        <f aca="false">(I29-H29)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I29-H29)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K29" s="51"/>
@@ -2884,7 +2884,7 @@
       <c r="H30" s="50"/>
       <c r="I30" s="50"/>
       <c r="J30" s="36" t="n">
-        <f aca="false">(I30-H30)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I30-H30)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K30" s="51"/>
@@ -2922,7 +2922,7 @@
       <c r="H31" s="50"/>
       <c r="I31" s="50"/>
       <c r="J31" s="36" t="n">
-        <f aca="false">(I31-H31)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I31-H31)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K31" s="51"/>
@@ -3489,7 +3489,7 @@
       <c r="H49" s="50"/>
       <c r="I49" s="50"/>
       <c r="J49" s="36" t="n">
-        <f aca="false">(I49-H49)/8.5*1.33</f>
+        <f aca="false">_xlfn.CEILING.MATH((I49-H49)/8.5*1.33,1)</f>
         <v>0</v>
       </c>
       <c r="K49" s="51"/>
